--- a/data/数据挖掘_知识点.xlsx
+++ b/data/数据挖掘_知识点.xlsx
@@ -1,21 +1,30 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
-  <bookViews>
-    <workbookView activeTab="0"/>
-  </bookViews>
-  <sheets>
-    <sheet name="知识点" r:id="rId3" sheetId="1"/>
-  </sheets>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Apache POI</Application>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-09-29T08:30:50Z</dcterms:created>
+  <dc:creator>Apache POI</dc:creator>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{5B77E7CE-EC58-BC6A-FAE8-886BEB80DBEB}" pid="2" name="5B77E7CEEC58BC6AFAE8886BEB80DBEB">
+    <vt:lpwstr>otCYQxs9Dbw2bUEn/Soxv9pYAoWsCRIsU8+gIbxzzmNcJN13+qHIPyWmbF9hFzPHyi2m8DLwi54E5OVVM5pJ0yGmgAiYTaR6oYUdYZxdjep6I9xviFUFZ9aTScfBW9OGqj1xtF2zu3uQZE7oWzNilAfp42pdVUQFfRm0DNPp9uTZh1dfZAjcuJTvRLnUOr3jNWqs9xIaEz0fTd+L2RlVcXUk2ddV9gJzBHB+0wJPT+InUobvWiv0QTg7Zbfjve794th+Gigu5Dbz/fy8TjRd4f4j97lgdoaq/29vg0UrzYQ+FzH8w7iq3Sdo6i59P1kceAdYfhf9sYr9TcoGpK6YWyce7JBGm1aGoq0l8VjfWXlPqnD7D+qkH8xL8gnry5rRDTnV1XwBNatyBXpxxHRdJQqKffmQ/zTZsW718vgpyvnl5xcix0zCraprhGvqSJLhp/jET+8u8eQwNhLZovLBbsTc1M1rUPfye9DcvrO68gSuULk8cHdf8oN/BA9bc2C0zS9+U6Nzmqia07fVehBpit8TQ7iXgtDtj0Aio2PhgfG52VzcMnrBWRCmwZCIwOpt5YLvPHn+obUGSO0ewgFH1kIHubaL1AJ25PU+tLWPggvj8DmzdsDFkkaICnV5rdvO</vt:lpwstr>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="2">
@@ -88,7 +97,19 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet name="知识点" r:id="rId3" sheetId="1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
